--- a/CANopen_COB_ID_Summary.xlsx
+++ b/CANopen_COB_ID_Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\HES-SO cours\Summer_school\SS2\DSS2_IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_57B7434B8BAFC993AFBDC32BD3CD67F6D24C48D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D2C94C-0E1A-477D-A68D-A373CBBD6C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>COB-ID</t>
   </si>
@@ -213,6 +213,18 @@
   </si>
   <si>
     <t>Le schéma montre 0x403 à deux endroits : un message de couple pour le Drive et un message de couple pour le Steering. Si ces deux messages utilisent réellement le même CAN-ID sur le même bus, il faut vérifier la configuration : deux producteurs ne devraient normalement pas émettre le même COB-ID.</t>
+  </si>
+  <si>
+    <t>0x334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">steering state machine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">steering state </t>
   </si>
 </sst>
 </file>
@@ -565,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -913,6 +925,24 @@
       </c>
       <c r="F17" s="2" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/CANopen_COB_ID_Summary.xlsx
+++ b/CANopen_COB_ID_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\HES-SO cours\Summer_school\SS2\DSS2_IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D2C94C-0E1A-477D-A68D-A373CBBD6C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39598CD9-C498-4764-A562-A3BB35A24709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>COB-ID</t>
   </si>
@@ -225,6 +225,27 @@
   </si>
   <si>
     <t xml:space="preserve">steering state </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gear transition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node 3 -- Control </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if gear is in transition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x190 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gear position </t>
+  </si>
+  <si>
+    <t xml:space="preserve">exact gear position </t>
   </si>
 </sst>
 </file>
@@ -577,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -943,6 +964,46 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/CANopen_COB_ID_Summary.xlsx
+++ b/CANopen_COB_ID_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\HES-SO cours\Summer_school\SS2\DSS2_IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39598CD9-C498-4764-A562-A3BB35A24709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45B0B20-EF4C-42DD-B95E-193C971CFDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CANopen COB-ID Summary'!$A$1:$F$17</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="83">
   <si>
     <t>COB-ID</t>
   </si>
@@ -246,6 +259,33 @@
   </si>
   <si>
     <t xml:space="preserve">exact gear position </t>
+  </si>
+  <si>
+    <t>0x514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botton DCDC </t>
+  </si>
+  <si>
+    <t>Bjorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">button shutdown </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x515 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus Voltage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bjorn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bus voltage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenghth </t>
   </si>
 </sst>
 </file>
@@ -598,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -608,7 +648,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,8 +667,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -648,7 +691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -668,7 +711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -688,7 +731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -708,7 +751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -728,7 +771,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -748,7 +791,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -768,7 +811,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -788,7 +831,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -808,7 +851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -828,7 +871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -848,7 +891,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
@@ -868,7 +911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -888,7 +931,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>53</v>
       </c>
@@ -908,7 +951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -928,7 +971,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -948,7 +991,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>63</v>
       </c>
@@ -965,8 +1008,11 @@
       <c r="F18" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
@@ -985,8 +1031,11 @@
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
@@ -1005,6 +1054,58 @@
       <c r="F20" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
